--- a/test/fixtures/xlsx/containers/containers.xlsx
+++ b/test/fixtures/xlsx/containers/containers.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="38">
   <si>
     <t xml:space="preserve">:table Shop</t>
   </si>
@@ -59,6 +59,15 @@
     <t xml:space="preserve">Bag.Prices.Value</t>
   </si>
   <si>
+    <t xml:space="preserve">Bag.Drops.Key</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bag.Drops.Value.ItemId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bag.Drops.Value.Count</t>
+  </si>
+  <si>
     <t xml:space="preserve">1</t>
   </si>
   <si>
@@ -71,6 +80,15 @@
     <t xml:space="preserve">100;120</t>
   </si>
   <si>
+    <t xml:space="preserve">1;2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101;102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1;3</t>
+  </si>
+  <si>
     <t xml:space="preserve">2</t>
   </si>
   <si>
@@ -83,6 +101,12 @@
     <t xml:space="preserve">90</t>
   </si>
   <si>
+    <t xml:space="preserve">101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5</t>
+  </si>
+  <si>
     <t xml:space="preserve">3</t>
   </si>
   <si>
@@ -95,7 +119,13 @@
     <t xml:space="preserve">100;120;140</t>
   </si>
   <si>
-    <t xml:space="preserve">5</t>
+    <t xml:space="preserve">1;2;3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101;102;103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1;3;5</t>
   </si>
 </sst>
 </file>
@@ -140,7 +170,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="B2:F11"/>
+  <dimension ref="B2:I11"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -167,6 +197,15 @@
       <c r="F3" t="s">
         <v>14</v>
       </c>
+      <c r="G3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="4">
       <c r="B4" t="s">
@@ -184,6 +223,15 @@
       <c r="F4" t="s">
         <v>12</v>
       </c>
+      <c r="G4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="5">
       <c r="B5" t="s">
@@ -201,6 +249,15 @@
       <c r="F5" t="s">
         <v>12</v>
       </c>
+      <c r="G5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="6">
       <c r="B6" t="s">
@@ -218,38 +275,65 @@
       <c r="F6" t="s">
         <v>9</v>
       </c>
+      <c r="G6" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" t="s">
+        <v>9</v>
+      </c>
+      <c r="I6" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="7">
       <c r="C7" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E7" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F7" t="s">
-        <v>18</v>
+        <v>21</v>
+      </c>
+      <c r="G7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="8">
       <c r="C8" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D8" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E8" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F8" t="s">
-        <v>22</v>
+        <v>28</v>
+      </c>
+      <c r="G8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" t="s">
+        <v>29</v>
+      </c>
+      <c r="I8" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="9">
       <c r="C9" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="D9" t="s">
         <v>12</v>
@@ -258,35 +342,62 @@
         <v>12</v>
       </c>
       <c r="F9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" t="s">
+        <v>12</v>
+      </c>
+      <c r="I9" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="10">
       <c r="C10" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="D10" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E10" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="F10" t="s">
-        <v>26</v>
+        <v>34</v>
+      </c>
+      <c r="G10" t="s">
+        <v>35</v>
+      </c>
+      <c r="H10" t="s">
+        <v>36</v>
+      </c>
+      <c r="I10" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="11">
       <c r="C11" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D11" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E11" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="F11" t="s">
-        <v>26</v>
+        <v>34</v>
+      </c>
+      <c r="G11" t="s">
+        <v>35</v>
+      </c>
+      <c r="H11" t="s">
+        <v>36</v>
+      </c>
+      <c r="I11" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
